--- a/data/config/portfolio_weights.xlsx
+++ b/data/config/portfolio_weights.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,15 +26,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -45,6 +52,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="008B1A1A"/>
         <bgColor rgb="008B1A1A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5ECD7"/>
+        <bgColor rgb="00F5ECD7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDE2C8"/>
+        <bgColor rgb="00EDE2C8"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,12 +85,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,11 +459,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -457,210 +485,254 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>EEM</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>iShares MSCI Emerging Markets ETF</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>15</v>
+      <c r="C2" s="2" t="n">
+        <v>15.36</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>VT</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Vanguard Total World Stock ETF</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>15</v>
+      <c r="C3" s="3" t="n">
+        <v>14.2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>ARTY</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Tuttle Capital AI ETF</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>iShares Future AI &amp; Tech ETF</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>9.08</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>IYZ</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>iShares U.S. Telecommunications ETF</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>7</v>
+      <c r="C5" s="3" t="n">
+        <v>7.26</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>EWT</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>iShares MSCI Taiwan ETF</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>7.02</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>EPOL</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>iShares MSCI Poland ETF</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>EWT</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>iShares MSCI Taiwan ETF</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>7</v>
+      <c r="C7" s="3" t="n">
+        <v>6.23</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>DTCR</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Global X Data Center &amp; Digital Infrastructure ETF</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>5.09</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>LIT</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Global X Lithium &amp; Battery Tech ETF</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>4.94</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>MCHI</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>iShares MSCI China ETF</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>HYDR</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Global X Hydrogen ETF</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>IAU</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>iShares Gold Trust</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>4.17</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>EWZ</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>iShares MSCI Brazil ETF</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="C13" s="3" t="n">
+        <v>4.06</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TAN</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Invesco Solar ETF</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>4.02</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>EWA</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>iShares MSCI Australia ETF</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MCHI</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>iShares MSCI China ETF</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>DTCR</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Global X Data Center &amp; Digital Infrastructure ETF</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>LIT</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Global X Lithium &amp; Battery Tech ETF</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>HYDR</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Global X Hydrogen ETF</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>IAU</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>iShares Gold Trust</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>iShares Silver Trust</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>CPER</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>United States Copper Index Fund</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr"/>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C15" s="2">
-        <f>SUM(C2:C14)</f>
-        <v/>
+      <c r="C18" s="5" t="n">
+        <v>100.02</v>
       </c>
     </row>
   </sheetData>
